--- a/reference/origins/product info/WA_Drinks_Regulatory_Audited.xlsx
+++ b/reference/origins/product info/WA_Drinks_Regulatory_Audited.xlsx
@@ -824,37 +824,32 @@
       <c r="J2" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="74">
-        <f>J2*$T2</f>
-        <v/>
+      <c r="K2" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L2" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="74">
-        <f>L2*$T2</f>
-        <v/>
+      <c r="M2" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N2" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="74">
-        <f>N2*$T2</f>
-        <v/>
+      <c r="O2" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P2" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="74">
-        <f>P2*$T2</f>
-        <v/>
+      <c r="Q2" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R2" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="74">
-        <f>R2*$T2</f>
-        <v/>
+      <c r="S2" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T2" s="75" t="n">
         <v>10</v>
@@ -887,18 +882,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA2" s="68">
-        <f>IF(ISNUMBER(Y2),ROUNDDOWN(Y2*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA2" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC2" s="76">
-        <f>IF(AND(ISNUMBER(AA2),ISNUMBER(T2),T2&gt;0),AA2/T2,"")</f>
-        <v/>
+      <c r="AC2" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD2" s="43" t="inlineStr">
         <is>
@@ -910,17 +903,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF2">
-        <f>"Net Vol. "&amp;TEXT(Y2,"0.##")&amp;" fl oz ("&amp;TEXT(AA2,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG2" s="76">
-        <f>IF(AND(ISNUMBER(Y2),ISNUMBER(T2),T2&gt;0),Y2/T2,"")</f>
-        <v/>
-      </c>
-      <c r="AH2">
-        <f>IF(AG2="","",TEXT(AG2,"0.##")&amp;" fl oz ("&amp;TEXT(AC2,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG2" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI2" s="43" t="inlineStr">
         <is>
@@ -982,37 +976,32 @@
       <c r="J3" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K3" s="74">
-        <f>J3*$T3</f>
-        <v/>
+      <c r="K3" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L3" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="74">
-        <f>L3*$T3</f>
-        <v/>
+      <c r="M3" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N3" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="74">
-        <f>N3*$T3</f>
-        <v/>
+      <c r="O3" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P3" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" s="74">
-        <f>P3*$T3</f>
-        <v/>
+      <c r="Q3" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R3" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S3" s="74">
-        <f>R3*$T3</f>
-        <v/>
+      <c r="S3" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T3" s="75" t="n">
         <v>10</v>
@@ -1045,18 +1034,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA3" s="68">
-        <f>IF(ISNUMBER(Y3),ROUNDDOWN(Y3*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA3" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC3" s="76">
-        <f>IF(AND(ISNUMBER(AA3),ISNUMBER(T3),T3&gt;0),AA3/T3,"")</f>
-        <v/>
+      <c r="AC3" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD3" s="43" t="inlineStr">
         <is>
@@ -1068,17 +1055,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF3">
-        <f>"Net Vol. "&amp;TEXT(Y3,"0.##")&amp;" fl oz ("&amp;TEXT(AA3,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG3" s="76">
-        <f>IF(AND(ISNUMBER(Y3),ISNUMBER(T3),T3&gt;0),Y3/T3,"")</f>
-        <v/>
-      </c>
-      <c r="AH3">
-        <f>IF(AG3="","",TEXT(AG3,"0.##")&amp;" fl oz ("&amp;TEXT(AC3,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG3" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI3" s="43" t="inlineStr">
         <is>
@@ -1140,37 +1128,32 @@
       <c r="J4" s="74" t="n">
         <v>1</v>
       </c>
-      <c r="K4" s="74">
-        <f>J4*$T4</f>
-        <v/>
+      <c r="K4" s="74" t="n">
+        <v>10</v>
       </c>
       <c r="L4" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="74">
-        <f>L4*$T4</f>
-        <v/>
+      <c r="M4" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N4" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="74">
-        <f>N4*$T4</f>
-        <v/>
+      <c r="O4" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P4" s="74" t="n">
         <v>20</v>
       </c>
-      <c r="Q4" s="74">
-        <f>P4*$T4</f>
-        <v/>
+      <c r="Q4" s="74" t="n">
+        <v>200</v>
       </c>
       <c r="R4" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S4" s="74">
-        <f>R4*$T4</f>
-        <v/>
+      <c r="S4" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T4" s="75" t="n">
         <v>10</v>
@@ -1203,18 +1186,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA4" s="68">
-        <f>IF(ISNUMBER(Y4),ROUNDDOWN(Y4*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA4" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC4" s="76">
-        <f>IF(AND(ISNUMBER(AA4),ISNUMBER(T4),T4&gt;0),AA4/T4,"")</f>
-        <v/>
+      <c r="AC4" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD4" s="43" t="inlineStr">
         <is>
@@ -1226,17 +1207,18 @@
           <t>https://greenrevolution.com/products/beverages/wildside/</t>
         </is>
       </c>
-      <c r="AF4">
-        <f>"Net Vol. "&amp;TEXT(Y4,"0.##")&amp;" fl oz ("&amp;TEXT(AA4,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG4" s="76">
-        <f>IF(AND(ISNUMBER(Y4),ISNUMBER(T4),T4&gt;0),Y4/T4,"")</f>
-        <v/>
-      </c>
-      <c r="AH4">
-        <f>IF(AG4="","",TEXT(AG4,"0.##")&amp;" fl oz ("&amp;TEXT(AC4,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG4" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI4" s="43" t="inlineStr">
         <is>
@@ -1298,37 +1280,32 @@
       <c r="J5" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="74">
-        <f>J5*$T5</f>
-        <v/>
+      <c r="K5" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L5" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="M5" s="74">
-        <f>L5*$T5</f>
-        <v/>
+      <c r="M5" s="74" t="n">
+        <v>25</v>
       </c>
       <c r="N5" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="74">
-        <f>N5*$T5</f>
-        <v/>
+      <c r="O5" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P5" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q5" s="74">
-        <f>P5*$T5</f>
-        <v/>
+      <c r="Q5" s="74" t="n">
+        <v>25</v>
       </c>
       <c r="R5" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S5" s="74">
-        <f>R5*$T5</f>
-        <v/>
+      <c r="S5" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T5" s="75" t="n">
         <v>10</v>
@@ -1361,18 +1338,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA5" s="68">
-        <f>IF(ISNUMBER(Y5),ROUNDDOWN(Y5*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA5" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC5" s="76">
-        <f>IF(AND(ISNUMBER(AA5),ISNUMBER(T5),T5&gt;0),AA5/T5,"")</f>
-        <v/>
+      <c r="AC5" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD5" s="43" t="inlineStr">
         <is>
@@ -1384,17 +1359,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF5">
-        <f>"Net Vol. "&amp;TEXT(Y5,"0.##")&amp;" fl oz ("&amp;TEXT(AA5,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG5" s="76">
-        <f>IF(AND(ISNUMBER(Y5),ISNUMBER(T5),T5&gt;0),Y5/T5,"")</f>
-        <v/>
-      </c>
-      <c r="AH5">
-        <f>IF(AG5="","",TEXT(AG5,"0.##")&amp;" fl oz ("&amp;TEXT(AC5,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG5" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI5" s="43" t="inlineStr">
         <is>
@@ -1456,37 +1432,32 @@
       <c r="J6" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="74">
-        <f>J6*$T6</f>
-        <v/>
+      <c r="K6" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L6" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="74">
-        <f>L6*$T6</f>
-        <v/>
+      <c r="M6" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N6" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="74">
-        <f>N6*$T6</f>
-        <v/>
+      <c r="O6" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P6" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" s="74">
-        <f>P6*$T6</f>
-        <v/>
+      <c r="Q6" s="74" t="n">
+        <v>50</v>
       </c>
       <c r="R6" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="S6" s="74">
-        <f>R6*$T6</f>
-        <v/>
+      <c r="S6" s="74" t="n">
+        <v>50</v>
       </c>
       <c r="T6" s="75" t="n">
         <v>10</v>
@@ -1519,18 +1490,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA6" s="68">
-        <f>IF(ISNUMBER(Y6),ROUNDDOWN(Y6*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA6" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC6" s="76">
-        <f>IF(AND(ISNUMBER(AA6),ISNUMBER(T6),T6&gt;0),AA6/T6,"")</f>
-        <v/>
+      <c r="AC6" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD6" s="43" t="inlineStr">
         <is>
@@ -1542,17 +1511,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF6">
-        <f>"Net Vol. "&amp;TEXT(Y6,"0.##")&amp;" fl oz ("&amp;TEXT(AA6,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG6" s="76">
-        <f>IF(AND(ISNUMBER(Y6),ISNUMBER(T6),T6&gt;0),Y6/T6,"")</f>
-        <v/>
-      </c>
-      <c r="AH6">
-        <f>IF(AG6="","",TEXT(AG6,"0.##")&amp;" fl oz ("&amp;TEXT(AC6,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG6" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI6" s="43" t="inlineStr">
         <is>
@@ -1614,37 +1584,32 @@
       <c r="J7" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K7" s="74">
-        <f>J7*$T7</f>
-        <v/>
+      <c r="K7" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="74">
-        <f>L7*$T7</f>
-        <v/>
+      <c r="M7" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="74" t="n">
         <v>0.5</v>
       </c>
-      <c r="O7" s="74">
-        <f>N7*$T7</f>
-        <v/>
+      <c r="O7" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="P7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="74">
-        <f>P7*$T7</f>
-        <v/>
+      <c r="Q7" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="74">
-        <f>R7*$T7</f>
-        <v/>
+      <c r="S7" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T7" s="75" t="n">
         <v>10</v>
@@ -1677,18 +1642,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA7" s="68">
-        <f>IF(ISNUMBER(Y7),ROUNDDOWN(Y7*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA7" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC7" s="76">
-        <f>IF(AND(ISNUMBER(AA7),ISNUMBER(T7),T7&gt;0),AA7/T7,"")</f>
-        <v/>
+      <c r="AC7" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD7" s="43" t="inlineStr">
         <is>
@@ -1700,17 +1663,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF7">
-        <f>"Net Vol. "&amp;TEXT(Y7,"0.##")&amp;" fl oz ("&amp;TEXT(AA7,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG7" s="76">
-        <f>IF(AND(ISNUMBER(Y7),ISNUMBER(T7),T7&gt;0),Y7/T7,"")</f>
-        <v/>
-      </c>
-      <c r="AH7">
-        <f>IF(AG7="","",TEXT(AG7,"0.##")&amp;" fl oz ("&amp;TEXT(AC7,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG7" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI7" s="43" t="inlineStr">
         <is>
@@ -1772,37 +1736,32 @@
       <c r="J8" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K8" s="74">
-        <f>J8*$T8</f>
-        <v/>
+      <c r="K8" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L8" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M8" s="74">
-        <f>L8*$T8</f>
-        <v/>
+      <c r="M8" s="74" t="n">
+        <v>50</v>
       </c>
       <c r="N8" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="O8" s="74">
-        <f>N8*$T8</f>
-        <v/>
+      <c r="O8" s="74" t="n">
+        <v>50</v>
       </c>
       <c r="P8" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="74">
-        <f>P8*$T8</f>
-        <v/>
+      <c r="Q8" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R8" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="74">
-        <f>R8*$T8</f>
-        <v/>
+      <c r="S8" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T8" s="75" t="n">
         <v>10</v>
@@ -1835,18 +1794,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA8" s="68">
-        <f>IF(ISNUMBER(Y8),ROUNDDOWN(Y8*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA8" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC8" s="76">
-        <f>IF(AND(ISNUMBER(AA8),ISNUMBER(T8),T8&gt;0),AA8/T8,"")</f>
-        <v/>
+      <c r="AC8" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD8" s="43" t="inlineStr">
         <is>
@@ -1858,17 +1815,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF8">
-        <f>"Net Vol. "&amp;TEXT(Y8,"0.##")&amp;" fl oz ("&amp;TEXT(AA8,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG8" s="76">
-        <f>IF(AND(ISNUMBER(Y8),ISNUMBER(T8),T8&gt;0),Y8/T8,"")</f>
-        <v/>
-      </c>
-      <c r="AH8">
-        <f>IF(AG8="","",TEXT(AG8,"0.##")&amp;" fl oz ("&amp;TEXT(AC8,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG8" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI8" s="43" t="inlineStr">
         <is>
@@ -1926,37 +1884,32 @@
       <c r="J9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="74">
-        <f>J9*$T9</f>
-        <v/>
+      <c r="K9" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L9" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M9" s="74">
-        <f>L9*$T9</f>
-        <v/>
+      <c r="M9" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O9" s="74">
-        <f>N9*$T9</f>
-        <v/>
+      <c r="O9" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" s="74">
-        <f>P9*$T9</f>
-        <v/>
+      <c r="Q9" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R9" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="74">
-        <f>R9*$T9</f>
-        <v/>
+      <c r="S9" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T9" s="75" t="n">
         <v>10</v>
@@ -1989,18 +1942,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA9" s="68">
-        <f>IF(ISNUMBER(Y9),ROUNDDOWN(Y9*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA9" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC9" s="76">
-        <f>IF(AND(ISNUMBER(AA9),ISNUMBER(T9),T9&gt;0),AA9/T9,"")</f>
-        <v/>
+      <c r="AC9" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD9" s="43" t="inlineStr">
         <is>
@@ -2012,17 +1963,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF9">
-        <f>"Net Vol. "&amp;TEXT(Y9,"0.##")&amp;" fl oz ("&amp;TEXT(AA9,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG9" s="76">
-        <f>IF(AND(ISNUMBER(Y9),ISNUMBER(T9),T9&gt;0),Y9/T9,"")</f>
-        <v/>
-      </c>
-      <c r="AH9">
-        <f>IF(AG9="","",TEXT(AG9,"0.##")&amp;" fl oz ("&amp;TEXT(AC9,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG9" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI9" s="43" t="inlineStr">
         <is>
@@ -2084,37 +2036,32 @@
       <c r="J10" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K10" s="74">
-        <f>J10*$T10</f>
-        <v/>
+      <c r="K10" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L10" s="74" t="n">
         <v>40</v>
       </c>
-      <c r="M10" s="74">
-        <f>L10*$T10</f>
-        <v/>
+      <c r="M10" s="74" t="n">
+        <v>400</v>
       </c>
       <c r="N10" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="74">
-        <f>N10*$T10</f>
-        <v/>
+      <c r="O10" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P10" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" s="74">
-        <f>P10*$T10</f>
-        <v/>
+      <c r="Q10" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R10" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="74">
-        <f>R10*$T10</f>
-        <v/>
+      <c r="S10" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T10" s="75" t="n">
         <v>10</v>
@@ -2147,18 +2094,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA10" s="68">
-        <f>IF(ISNUMBER(Y10),ROUNDDOWN(Y10*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA10" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC10" s="76">
-        <f>IF(AND(ISNUMBER(AA10),ISNUMBER(T10),T10&gt;0),AA10/T10,"")</f>
-        <v/>
+      <c r="AC10" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD10" s="43" t="inlineStr">
         <is>
@@ -2170,17 +2115,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF10">
-        <f>"Net Vol. "&amp;TEXT(Y10,"0.##")&amp;" fl oz ("&amp;TEXT(AA10,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG10" s="76">
-        <f>IF(AND(ISNUMBER(Y10),ISNUMBER(T10),T10&gt;0),Y10/T10,"")</f>
-        <v/>
-      </c>
-      <c r="AH10">
-        <f>IF(AG10="","",TEXT(AG10,"0.##")&amp;" fl oz ("&amp;TEXT(AC10,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG10" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI10" s="43" t="inlineStr">
         <is>
@@ -2238,37 +2184,32 @@
       <c r="J11" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="74">
-        <f>J11*$T11</f>
-        <v/>
+      <c r="K11" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L11" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="74">
-        <f>L11*$T11</f>
-        <v/>
+      <c r="M11" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N11" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="74">
-        <f>N11*$T11</f>
-        <v/>
+      <c r="O11" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P11" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" s="74">
-        <f>P11*$T11</f>
-        <v/>
+      <c r="Q11" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R11" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S11" s="74">
-        <f>R11*$T11</f>
-        <v/>
+      <c r="S11" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T11" s="75" t="n">
         <v>10</v>
@@ -2301,18 +2242,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA11" s="68">
-        <f>IF(ISNUMBER(Y11),ROUNDDOWN(Y11*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA11" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC11" s="76">
-        <f>IF(AND(ISNUMBER(AA11),ISNUMBER(T11),T11&gt;0),AA11/T11,"")</f>
-        <v/>
+      <c r="AC11" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD11" s="43" t="inlineStr">
         <is>
@@ -2324,17 +2263,18 @@
           <t>https://greenrevolution.com/products/beverages/</t>
         </is>
       </c>
-      <c r="AF11">
-        <f>"Net Vol. "&amp;TEXT(Y11,"0.##")&amp;" fl oz ("&amp;TEXT(AA11,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG11" s="76">
-        <f>IF(AND(ISNUMBER(Y11),ISNUMBER(T11),T11&gt;0),Y11/T11,"")</f>
-        <v/>
-      </c>
-      <c r="AH11">
-        <f>IF(AG11="","",TEXT(AG11,"0.##")&amp;" fl oz ("&amp;TEXT(AC11,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG11" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI11" s="43" t="inlineStr">
         <is>
@@ -2396,37 +2336,32 @@
       <c r="J12" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="K12" s="74">
-        <f>J12*$T12</f>
-        <v/>
+      <c r="K12" s="74" t="n">
+        <v>2.5</v>
       </c>
       <c r="L12" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M12" s="74">
-        <f>L12*$T12</f>
-        <v/>
+      <c r="M12" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N12" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="74">
-        <f>N12*$T12</f>
-        <v/>
+      <c r="O12" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P12" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="74">
-        <f>P12*$T12</f>
-        <v/>
+      <c r="Q12" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R12" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="74">
-        <f>R12*$T12</f>
-        <v/>
+      <c r="S12" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T12" s="75" t="n">
         <v>1</v>
@@ -2459,18 +2394,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA12" s="68">
-        <f>IF(ISNUMBER(Y12),ROUNDDOWN(Y12*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA12" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC12" s="76">
-        <f>IF(AND(ISNUMBER(AA12),ISNUMBER(T12),T12&gt;0),AA12/T12,"")</f>
-        <v/>
+      <c r="AC12" s="76" t="n">
+        <v>354</v>
       </c>
       <c r="AD12" s="43" t="inlineStr">
         <is>
@@ -2482,17 +2415,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF12">
-        <f>"Net Vol. "&amp;TEXT(Y12,"0.##")&amp;" fl oz ("&amp;TEXT(AA12,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG12" s="76">
-        <f>IF(AND(ISNUMBER(Y12),ISNUMBER(T12),T12&gt;0),Y12/T12,"")</f>
-        <v/>
-      </c>
-      <c r="AH12">
-        <f>IF(AG12="","",TEXT(AG12,"0.##")&amp;" fl oz ("&amp;TEXT(AC12,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG12" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>12. fl oz (354. mL)</t>
+        </is>
       </c>
       <c r="AI12" s="43" t="inlineStr">
         <is>
@@ -2554,37 +2488,32 @@
       <c r="J13" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="74">
-        <f>J13*$T13</f>
-        <v/>
+      <c r="K13" s="74" t="n">
+        <v>2.5</v>
       </c>
       <c r="L13" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="74">
-        <f>L13*$T13</f>
-        <v/>
+      <c r="M13" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N13" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="74">
-        <f>N13*$T13</f>
-        <v/>
+      <c r="O13" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P13" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" s="74">
-        <f>P13*$T13</f>
-        <v/>
+      <c r="Q13" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="74">
-        <f>R13*$T13</f>
-        <v/>
+      <c r="S13" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T13" s="75" t="n">
         <v>1</v>
@@ -2617,18 +2546,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA13" s="68">
-        <f>IF(ISNUMBER(Y13),ROUNDDOWN(Y13*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA13" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC13" s="76">
-        <f>IF(AND(ISNUMBER(AA13),ISNUMBER(T13),T13&gt;0),AA13/T13,"")</f>
-        <v/>
+      <c r="AC13" s="76" t="n">
+        <v>354</v>
       </c>
       <c r="AD13" s="43" t="inlineStr">
         <is>
@@ -2640,17 +2567,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF13">
-        <f>"Net Vol. "&amp;TEXT(Y13,"0.##")&amp;" fl oz ("&amp;TEXT(AA13,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG13" s="76">
-        <f>IF(AND(ISNUMBER(Y13),ISNUMBER(T13),T13&gt;0),Y13/T13,"")</f>
-        <v/>
-      </c>
-      <c r="AH13">
-        <f>IF(AG13="","",TEXT(AG13,"0.##")&amp;" fl oz ("&amp;TEXT(AC13,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG13" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>12. fl oz (354. mL)</t>
+        </is>
       </c>
       <c r="AI13" s="43" t="inlineStr">
         <is>
@@ -2712,37 +2640,32 @@
       <c r="J14" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="K14" s="74">
-        <f>J14*$T14</f>
-        <v/>
+      <c r="K14" s="74" t="n">
+        <v>2.5</v>
       </c>
       <c r="L14" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M14" s="74">
-        <f>L14*$T14</f>
-        <v/>
+      <c r="M14" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N14" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="74">
-        <f>N14*$T14</f>
-        <v/>
+      <c r="O14" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P14" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" s="74">
-        <f>P14*$T14</f>
-        <v/>
+      <c r="Q14" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R14" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="74">
-        <f>R14*$T14</f>
-        <v/>
+      <c r="S14" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T14" s="75" t="n">
         <v>1</v>
@@ -2775,18 +2698,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA14" s="68">
-        <f>IF(ISNUMBER(Y14),ROUNDDOWN(Y14*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA14" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC14" s="76">
-        <f>IF(AND(ISNUMBER(AA14),ISNUMBER(T14),T14&gt;0),AA14/T14,"")</f>
-        <v/>
+      <c r="AC14" s="76" t="n">
+        <v>354</v>
       </c>
       <c r="AD14" s="43" t="inlineStr">
         <is>
@@ -2798,17 +2719,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF14">
-        <f>"Net Vol. "&amp;TEXT(Y14,"0.##")&amp;" fl oz ("&amp;TEXT(AA14,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG14" s="76">
-        <f>IF(AND(ISNUMBER(Y14),ISNUMBER(T14),T14&gt;0),Y14/T14,"")</f>
-        <v/>
-      </c>
-      <c r="AH14">
-        <f>IF(AG14="","",TEXT(AG14,"0.##")&amp;" fl oz ("&amp;TEXT(AC14,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG14" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>12. fl oz (354. mL)</t>
+        </is>
       </c>
       <c r="AI14" s="43" t="inlineStr">
         <is>
@@ -2870,37 +2792,32 @@
       <c r="J15" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K15" s="74">
-        <f>J15*$T15</f>
-        <v/>
+      <c r="K15" s="74" t="n">
+        <v>10</v>
       </c>
       <c r="L15" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="74">
-        <f>L15*$T15</f>
-        <v/>
+      <c r="M15" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N15" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="74">
-        <f>N15*$T15</f>
-        <v/>
+      <c r="O15" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P15" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" s="74">
-        <f>P15*$T15</f>
-        <v/>
+      <c r="Q15" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R15" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="74">
-        <f>R15*$T15</f>
-        <v/>
+      <c r="S15" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T15" s="75" t="n">
         <v>1</v>
@@ -2933,18 +2850,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA15" s="68">
-        <f>IF(ISNUMBER(Y15),ROUNDDOWN(Y15*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA15" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC15" s="76">
-        <f>IF(AND(ISNUMBER(AA15),ISNUMBER(T15),T15&gt;0),AA15/T15,"")</f>
-        <v/>
+      <c r="AC15" s="76" t="n">
+        <v>473</v>
       </c>
       <c r="AD15" s="43" t="inlineStr">
         <is>
@@ -2956,17 +2871,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF15">
-        <f>"Net Vol. "&amp;TEXT(Y15,"0.##")&amp;" fl oz ("&amp;TEXT(AA15,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG15" s="76">
-        <f>IF(AND(ISNUMBER(Y15),ISNUMBER(T15),T15&gt;0),Y15/T15,"")</f>
-        <v/>
-      </c>
-      <c r="AH15">
-        <f>IF(AG15="","",TEXT(AG15,"0.##")&amp;" fl oz ("&amp;TEXT(AC15,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG15" s="76" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>16. fl oz (473. mL)</t>
+        </is>
       </c>
       <c r="AI15" s="43" t="inlineStr">
         <is>
@@ -3028,37 +2944,32 @@
       <c r="J16" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K16" s="74">
-        <f>J16*$T16</f>
-        <v/>
+      <c r="K16" s="74" t="n">
+        <v>10</v>
       </c>
       <c r="L16" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M16" s="74">
-        <f>L16*$T16</f>
-        <v/>
+      <c r="M16" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N16" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="74">
-        <f>N16*$T16</f>
-        <v/>
+      <c r="O16" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P16" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" s="74">
-        <f>P16*$T16</f>
-        <v/>
+      <c r="Q16" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R16" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="74">
-        <f>R16*$T16</f>
-        <v/>
+      <c r="S16" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T16" s="75" t="n">
         <v>1</v>
@@ -3091,18 +3002,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA16" s="68">
-        <f>IF(ISNUMBER(Y16),ROUNDDOWN(Y16*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA16" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC16" s="76">
-        <f>IF(AND(ISNUMBER(AA16),ISNUMBER(T16),T16&gt;0),AA16/T16,"")</f>
-        <v/>
+      <c r="AC16" s="76" t="n">
+        <v>473</v>
       </c>
       <c r="AD16" s="43" t="inlineStr">
         <is>
@@ -3114,17 +3023,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF16">
-        <f>"Net Vol. "&amp;TEXT(Y16,"0.##")&amp;" fl oz ("&amp;TEXT(AA16,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG16" s="76">
-        <f>IF(AND(ISNUMBER(Y16),ISNUMBER(T16),T16&gt;0),Y16/T16,"")</f>
-        <v/>
-      </c>
-      <c r="AH16">
-        <f>IF(AG16="","",TEXT(AG16,"0.##")&amp;" fl oz ("&amp;TEXT(AC16,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG16" s="76" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>16. fl oz (473. mL)</t>
+        </is>
       </c>
       <c r="AI16" s="43" t="inlineStr">
         <is>
@@ -3186,37 +3096,32 @@
       <c r="J17" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K17" s="74">
-        <f>J17*$T17</f>
-        <v/>
+      <c r="K17" s="74" t="n">
+        <v>10</v>
       </c>
       <c r="L17" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M17" s="74">
-        <f>L17*$T17</f>
-        <v/>
+      <c r="M17" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N17" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="74">
-        <f>N17*$T17</f>
-        <v/>
+      <c r="O17" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P17" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" s="74">
-        <f>P17*$T17</f>
-        <v/>
+      <c r="Q17" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R17" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S17" s="74">
-        <f>R17*$T17</f>
-        <v/>
+      <c r="S17" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T17" s="75" t="n">
         <v>1</v>
@@ -3249,18 +3154,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA17" s="68">
-        <f>IF(ISNUMBER(Y17),ROUNDDOWN(Y17*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA17" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC17" s="76">
-        <f>IF(AND(ISNUMBER(AA17),ISNUMBER(T17),T17&gt;0),AA17/T17,"")</f>
-        <v/>
+      <c r="AC17" s="76" t="n">
+        <v>473</v>
       </c>
       <c r="AD17" s="43" t="inlineStr">
         <is>
@@ -3272,17 +3175,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF17">
-        <f>"Net Vol. "&amp;TEXT(Y17,"0.##")&amp;" fl oz ("&amp;TEXT(AA17,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG17" s="76">
-        <f>IF(AND(ISNUMBER(Y17),ISNUMBER(T17),T17&gt;0),Y17/T17,"")</f>
-        <v/>
-      </c>
-      <c r="AH17">
-        <f>IF(AG17="","",TEXT(AG17,"0.##")&amp;" fl oz ("&amp;TEXT(AC17,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG17" s="76" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>16. fl oz (473. mL)</t>
+        </is>
       </c>
       <c r="AI17" s="43" t="inlineStr">
         <is>
@@ -3340,37 +3244,32 @@
       <c r="J18" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="74">
-        <f>J18*$T18</f>
-        <v/>
+      <c r="K18" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="L18" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="74">
-        <f>L18*$T18</f>
-        <v/>
+      <c r="M18" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N18" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="74">
-        <f>N18*$T18</f>
-        <v/>
+      <c r="O18" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P18" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="74">
-        <f>P18*$T18</f>
-        <v/>
+      <c r="Q18" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R18" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="74">
-        <f>R18*$T18</f>
-        <v/>
+      <c r="S18" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T18" s="75" t="n">
         <v>1</v>
@@ -3403,18 +3302,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA18" s="68">
-        <f>IF(ISNUMBER(Y18),ROUNDDOWN(Y18*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA18" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC18" s="76">
-        <f>IF(AND(ISNUMBER(AA18),ISNUMBER(T18),T18&gt;0),AA18/T18,"")</f>
-        <v/>
+      <c r="AC18" s="76" t="n">
+        <v>354</v>
       </c>
       <c r="AD18" s="43" t="inlineStr">
         <is>
@@ -3426,17 +3323,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF18">
-        <f>"Net Vol. "&amp;TEXT(Y18,"0.##")&amp;" fl oz ("&amp;TEXT(AA18,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG18" s="76">
-        <f>IF(AND(ISNUMBER(Y18),ISNUMBER(T18),T18&gt;0),Y18/T18,"")</f>
-        <v/>
-      </c>
-      <c r="AH18">
-        <f>IF(AG18="","",TEXT(AG18,"0.##")&amp;" fl oz ("&amp;TEXT(AC18,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG18" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>12. fl oz (354. mL)</t>
+        </is>
       </c>
       <c r="AI18" s="43" t="inlineStr">
         <is>
@@ -3494,37 +3392,32 @@
       <c r="J19" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="74">
-        <f>J19*$T19</f>
-        <v/>
+      <c r="K19" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L19" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="74">
-        <f>L19*$T19</f>
-        <v/>
+      <c r="M19" s="74" t="n">
+        <v>5</v>
       </c>
       <c r="N19" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="74">
-        <f>N19*$T19</f>
-        <v/>
+      <c r="O19" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P19" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="74">
-        <f>P19*$T19</f>
-        <v/>
+      <c r="Q19" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R19" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="74">
-        <f>R19*$T19</f>
-        <v/>
+      <c r="S19" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T19" s="75" t="n">
         <v>1</v>
@@ -3557,18 +3450,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA19" s="68">
-        <f>IF(ISNUMBER(Y19),ROUNDDOWN(Y19*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA19" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC19" s="76">
-        <f>IF(AND(ISNUMBER(AA19),ISNUMBER(T19),T19&gt;0),AA19/T19,"")</f>
-        <v/>
+      <c r="AC19" s="76" t="n">
+        <v>354</v>
       </c>
       <c r="AD19" s="43" t="inlineStr">
         <is>
@@ -3580,17 +3471,18 @@
           <t>https://www.drinksungaze.com/find-sungaze</t>
         </is>
       </c>
-      <c r="AF19">
-        <f>"Net Vol. "&amp;TEXT(Y19,"0.##")&amp;" fl oz ("&amp;TEXT(AA19,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG19" s="76">
-        <f>IF(AND(ISNUMBER(Y19),ISNUMBER(T19),T19&gt;0),Y19/T19,"")</f>
-        <v/>
-      </c>
-      <c r="AH19">
-        <f>IF(AG19="","",TEXT(AG19,"0.##")&amp;" fl oz ("&amp;TEXT(AC19,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG19" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>12. fl oz (354. mL)</t>
+        </is>
       </c>
       <c r="AI19" s="43" t="inlineStr">
         <is>
@@ -3648,37 +3540,32 @@
       <c r="J20" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K20" s="74">
-        <f>J20*$T20</f>
-        <v/>
+      <c r="K20" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L20" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="74">
-        <f>L20*$T20</f>
-        <v/>
+      <c r="M20" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N20" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="74">
-        <f>N20*$T20</f>
-        <v/>
+      <c r="O20" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P20" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" s="74">
-        <f>P20*$T20</f>
-        <v/>
+      <c r="Q20" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R20" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="74">
-        <f>R20*$T20</f>
-        <v/>
+      <c r="S20" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T20" s="75" t="n">
         <v>10</v>
@@ -3711,18 +3598,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA20" s="68">
-        <f>IF(ISNUMBER(Y20),ROUNDDOWN(Y20*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA20" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC20" s="76">
-        <f>IF(AND(ISNUMBER(AA20),ISNUMBER(T20),T20&gt;0),AA20/T20,"")</f>
-        <v/>
+      <c r="AC20" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD20" s="43" t="inlineStr">
         <is>
@@ -3734,17 +3619,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF20">
-        <f>"Net Vol. "&amp;TEXT(Y20,"0.##")&amp;" fl oz ("&amp;TEXT(AA20,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG20" s="76">
-        <f>IF(AND(ISNUMBER(Y20),ISNUMBER(T20),T20&gt;0),Y20/T20,"")</f>
-        <v/>
-      </c>
-      <c r="AH20">
-        <f>IF(AG20="","",TEXT(AG20,"0.##")&amp;" fl oz ("&amp;TEXT(AC20,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG20" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI20" s="43" t="inlineStr">
         <is>
@@ -3802,37 +3688,32 @@
       <c r="J21" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K21" s="74">
-        <f>J21*$T21</f>
-        <v/>
+      <c r="K21" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L21" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="74">
-        <f>L21*$T21</f>
-        <v/>
+      <c r="M21" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N21" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="74">
-        <f>N21*$T21</f>
-        <v/>
+      <c r="O21" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P21" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="74">
-        <f>P21*$T21</f>
-        <v/>
+      <c r="Q21" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R21" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="74">
-        <f>R21*$T21</f>
-        <v/>
+      <c r="S21" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T21" s="75" t="n">
         <v>10</v>
@@ -3865,18 +3746,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA21" s="68">
-        <f>IF(ISNUMBER(Y21),ROUNDDOWN(Y21*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA21" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC21" s="76">
-        <f>IF(AND(ISNUMBER(AA21),ISNUMBER(T21),T21&gt;0),AA21/T21,"")</f>
-        <v/>
+      <c r="AC21" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD21" s="43" t="inlineStr">
         <is>
@@ -3888,17 +3767,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF21">
-        <f>"Net Vol. "&amp;TEXT(Y21,"0.##")&amp;" fl oz ("&amp;TEXT(AA21,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG21" s="76">
-        <f>IF(AND(ISNUMBER(Y21),ISNUMBER(T21),T21&gt;0),Y21/T21,"")</f>
-        <v/>
-      </c>
-      <c r="AH21">
-        <f>IF(AG21="","",TEXT(AG21,"0.##")&amp;" fl oz ("&amp;TEXT(AC21,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG21" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI21" s="43" t="inlineStr">
         <is>
@@ -3956,37 +3836,32 @@
       <c r="J22" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K22" s="74">
-        <f>J22*$T22</f>
-        <v/>
+      <c r="K22" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L22" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="74">
-        <f>L22*$T22</f>
-        <v/>
+      <c r="M22" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N22" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O22" s="74">
-        <f>N22*$T22</f>
-        <v/>
+      <c r="O22" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P22" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="74">
-        <f>P22*$T22</f>
-        <v/>
+      <c r="Q22" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R22" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="74">
-        <f>R22*$T22</f>
-        <v/>
+      <c r="S22" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T22" s="75" t="n">
         <v>10</v>
@@ -4019,18 +3894,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA22" s="68">
-        <f>IF(ISNUMBER(Y22),ROUNDDOWN(Y22*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA22" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC22" s="76">
-        <f>IF(AND(ISNUMBER(AA22),ISNUMBER(T22),T22&gt;0),AA22/T22,"")</f>
-        <v/>
+      <c r="AC22" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD22" s="43" t="inlineStr">
         <is>
@@ -4042,17 +3915,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF22">
-        <f>"Net Vol. "&amp;TEXT(Y22,"0.##")&amp;" fl oz ("&amp;TEXT(AA22,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG22" s="76">
-        <f>IF(AND(ISNUMBER(Y22),ISNUMBER(T22),T22&gt;0),Y22/T22,"")</f>
-        <v/>
-      </c>
-      <c r="AH22">
-        <f>IF(AG22="","",TEXT(AG22,"0.##")&amp;" fl oz ("&amp;TEXT(AC22,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG22" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI22" s="43" t="inlineStr">
         <is>
@@ -4110,37 +3984,32 @@
       <c r="J23" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K23" s="74">
-        <f>J23*$T23</f>
-        <v/>
+      <c r="K23" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L23" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="74">
-        <f>L23*$T23</f>
-        <v/>
+      <c r="M23" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N23" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="74">
-        <f>N23*$T23</f>
-        <v/>
+      <c r="O23" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P23" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="74">
-        <f>P23*$T23</f>
-        <v/>
+      <c r="Q23" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R23" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="74">
-        <f>R23*$T23</f>
-        <v/>
+      <c r="S23" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T23" s="75" t="n">
         <v>10</v>
@@ -4173,18 +4042,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA23" s="68">
-        <f>IF(ISNUMBER(Y23),ROUNDDOWN(Y23*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA23" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC23" s="76">
-        <f>IF(AND(ISNUMBER(AA23),ISNUMBER(T23),T23&gt;0),AA23/T23,"")</f>
-        <v/>
+      <c r="AC23" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD23" s="43" t="inlineStr">
         <is>
@@ -4196,17 +4063,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF23">
-        <f>"Net Vol. "&amp;TEXT(Y23,"0.##")&amp;" fl oz ("&amp;TEXT(AA23,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG23" s="76">
-        <f>IF(AND(ISNUMBER(Y23),ISNUMBER(T23),T23&gt;0),Y23/T23,"")</f>
-        <v/>
-      </c>
-      <c r="AH23">
-        <f>IF(AG23="","",TEXT(AG23,"0.##")&amp;" fl oz ("&amp;TEXT(AC23,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG23" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI23" s="43" t="inlineStr">
         <is>
@@ -4264,37 +4132,32 @@
       <c r="J24" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K24" s="74">
-        <f>J24*$T24</f>
-        <v/>
+      <c r="K24" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L24" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="74">
-        <f>L24*$T24</f>
-        <v/>
+      <c r="M24" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N24" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="74">
-        <f>N24*$T24</f>
-        <v/>
+      <c r="O24" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P24" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" s="74">
-        <f>P24*$T24</f>
-        <v/>
+      <c r="Q24" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R24" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="74">
-        <f>R24*$T24</f>
-        <v/>
+      <c r="S24" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T24" s="75" t="n">
         <v>10</v>
@@ -4327,18 +4190,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA24" s="68">
-        <f>IF(ISNUMBER(Y24),ROUNDDOWN(Y24*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA24" s="68" t="n">
+        <v>59</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC24" s="76">
-        <f>IF(AND(ISNUMBER(AA24),ISNUMBER(T24),T24&gt;0),AA24/T24,"")</f>
-        <v/>
+      <c r="AC24" s="76" t="n">
+        <v>5.9</v>
       </c>
       <c r="AD24" s="43" t="inlineStr">
         <is>
@@ -4350,17 +4211,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF24">
-        <f>"Net Vol. "&amp;TEXT(Y24,"0.##")&amp;" fl oz ("&amp;TEXT(AA24,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG24" s="76">
-        <f>IF(AND(ISNUMBER(Y24),ISNUMBER(T24),T24&gt;0),Y24/T24,"")</f>
-        <v/>
-      </c>
-      <c r="AH24">
-        <f>IF(AG24="","",TEXT(AG24,"0.##")&amp;" fl oz ("&amp;TEXT(AC24,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Net Vol. 2. fl oz (59. mL)</t>
+        </is>
+      </c>
+      <c r="AG24" s="76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>0.2 fl oz (5.9 mL)</t>
+        </is>
       </c>
       <c r="AI24" s="43" t="inlineStr">
         <is>
@@ -4418,37 +4280,32 @@
       <c r="J25" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K25" s="74">
-        <f>J25*$T25</f>
-        <v/>
+      <c r="K25" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L25" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="74">
-        <f>L25*$T25</f>
-        <v/>
+      <c r="M25" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N25" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="74">
-        <f>N25*$T25</f>
-        <v/>
+      <c r="O25" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P25" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" s="74">
-        <f>P25*$T25</f>
-        <v/>
+      <c r="Q25" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R25" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="74">
-        <f>R25*$T25</f>
-        <v/>
+      <c r="S25" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T25" s="75" t="n">
         <v>10</v>
@@ -4481,18 +4338,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA25" s="68">
-        <f>IF(ISNUMBER(Y25),ROUNDDOWN(Y25*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA25" s="68" t="n">
+        <v>198</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC25" s="76">
-        <f>IF(AND(ISNUMBER(AA25),ISNUMBER(T25),T25&gt;0),AA25/T25,"")</f>
-        <v/>
+      <c r="AC25" s="76" t="n">
+        <v>19.8</v>
       </c>
       <c r="AD25" s="43" t="inlineStr">
         <is>
@@ -4504,17 +4359,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF25">
-        <f>"Net Vol. "&amp;TEXT(Y25,"0.##")&amp;" fl oz ("&amp;TEXT(AA25,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG25" s="76">
-        <f>IF(AND(ISNUMBER(Y25),ISNUMBER(T25),T25&gt;0),Y25/T25,"")</f>
-        <v/>
-      </c>
-      <c r="AH25">
-        <f>IF(AG25="","",TEXT(AG25,"0.##")&amp;" fl oz ("&amp;TEXT(AC25,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Net Vol. 6.7 fl oz (198. mL)</t>
+        </is>
+      </c>
+      <c r="AG25" s="76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>0.67 fl oz (19.8 mL)</t>
+        </is>
       </c>
       <c r="AI25" s="43" t="inlineStr">
         <is>
@@ -4572,37 +4428,32 @@
       <c r="J26" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K26" s="74">
-        <f>J26*$T26</f>
-        <v/>
+      <c r="K26" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L26" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="74">
-        <f>L26*$T26</f>
-        <v/>
+      <c r="M26" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N26" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="74">
-        <f>N26*$T26</f>
-        <v/>
+      <c r="O26" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P26" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" s="74">
-        <f>P26*$T26</f>
-        <v/>
+      <c r="Q26" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R26" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="74">
-        <f>R26*$T26</f>
-        <v/>
+      <c r="S26" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T26" s="75" t="n">
         <v>10</v>
@@ -4635,18 +4486,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA26" s="68">
-        <f>IF(ISNUMBER(Y26),ROUNDDOWN(Y26*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA26" s="68" t="n">
+        <v>198</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC26" s="76">
-        <f>IF(AND(ISNUMBER(AA26),ISNUMBER(T26),T26&gt;0),AA26/T26,"")</f>
-        <v/>
+      <c r="AC26" s="76" t="n">
+        <v>19.8</v>
       </c>
       <c r="AD26" s="43" t="inlineStr">
         <is>
@@ -4658,17 +4507,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF26">
-        <f>"Net Vol. "&amp;TEXT(Y26,"0.##")&amp;" fl oz ("&amp;TEXT(AA26,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG26" s="76">
-        <f>IF(AND(ISNUMBER(Y26),ISNUMBER(T26),T26&gt;0),Y26/T26,"")</f>
-        <v/>
-      </c>
-      <c r="AH26">
-        <f>IF(AG26="","",TEXT(AG26,"0.##")&amp;" fl oz ("&amp;TEXT(AC26,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Net Vol. 6.7 fl oz (198. mL)</t>
+        </is>
+      </c>
+      <c r="AG26" s="76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>0.67 fl oz (19.8 mL)</t>
+        </is>
       </c>
       <c r="AI26" s="43" t="inlineStr">
         <is>
@@ -4726,37 +4576,32 @@
       <c r="J27" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="74">
-        <f>J27*$T27</f>
-        <v/>
+      <c r="K27" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L27" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="74">
-        <f>L27*$T27</f>
-        <v/>
+      <c r="M27" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N27" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O27" s="74">
-        <f>N27*$T27</f>
-        <v/>
+      <c r="O27" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P27" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" s="74">
-        <f>P27*$T27</f>
-        <v/>
+      <c r="Q27" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R27" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="74">
-        <f>R27*$T27</f>
-        <v/>
+      <c r="S27" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T27" s="75" t="n">
         <v>10</v>
@@ -4789,18 +4634,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA27" s="68">
-        <f>IF(ISNUMBER(Y27),ROUNDDOWN(Y27*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA27" s="68" t="n">
+        <v>198</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC27" s="76">
-        <f>IF(AND(ISNUMBER(AA27),ISNUMBER(T27),T27&gt;0),AA27/T27,"")</f>
-        <v/>
+      <c r="AC27" s="76" t="n">
+        <v>19.8</v>
       </c>
       <c r="AD27" s="43" t="inlineStr">
         <is>
@@ -4812,17 +4655,18 @@
           <t>https://www.nevisbrands.com/major</t>
         </is>
       </c>
-      <c r="AF27">
-        <f>"Net Vol. "&amp;TEXT(Y27,"0.##")&amp;" fl oz ("&amp;TEXT(AA27,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG27" s="76">
-        <f>IF(AND(ISNUMBER(Y27),ISNUMBER(T27),T27&gt;0),Y27/T27,"")</f>
-        <v/>
-      </c>
-      <c r="AH27">
-        <f>IF(AG27="","",TEXT(AG27,"0.##")&amp;" fl oz ("&amp;TEXT(AC27,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Net Vol. 6.7 fl oz (198. mL)</t>
+        </is>
+      </c>
+      <c r="AG27" s="76" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>0.67 fl oz (19.8 mL)</t>
+        </is>
       </c>
       <c r="AI27" s="43" t="inlineStr">
         <is>
@@ -4880,37 +4724,32 @@
       <c r="J28" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K28" s="74">
-        <f>J28*$T28</f>
-        <v/>
+      <c r="K28" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L28" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="74">
-        <f>L28*$T28</f>
-        <v/>
+      <c r="M28" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N28" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="74">
-        <f>N28*$T28</f>
-        <v/>
+      <c r="O28" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P28" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" s="74">
-        <f>P28*$T28</f>
-        <v/>
+      <c r="Q28" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R28" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="74">
-        <f>R28*$T28</f>
-        <v/>
+      <c r="S28" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T28" s="75" t="n">
         <v>10</v>
@@ -4966,7 +4805,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG28" s="76" t="n">
@@ -5033,37 +4872,32 @@
       <c r="J29" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="74">
-        <f>J29*$T29</f>
-        <v/>
+      <c r="K29" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L29" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M29" s="74">
-        <f>L29*$T29</f>
-        <v/>
+      <c r="M29" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N29" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="74">
-        <f>N29*$T29</f>
-        <v/>
+      <c r="O29" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" s="74">
-        <f>P29*$T29</f>
-        <v/>
+      <c r="Q29" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R29" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="74">
-        <f>R29*$T29</f>
-        <v/>
+      <c r="S29" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T29" s="75" t="n">
         <v>10</v>
@@ -5119,7 +4953,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG29" s="76" t="n">
@@ -5190,37 +5024,32 @@
       <c r="J30" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K30" s="74">
-        <f>J30*$T30</f>
-        <v/>
+      <c r="K30" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L30" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M30" s="74">
-        <f>L30*$T30</f>
-        <v/>
+      <c r="M30" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N30" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="74">
-        <f>N30*$T30</f>
-        <v/>
+      <c r="O30" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P30" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" s="74">
-        <f>P30*$T30</f>
-        <v/>
+      <c r="Q30" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R30" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="74">
-        <f>R30*$T30</f>
-        <v/>
+      <c r="S30" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T30" s="75" t="n">
         <v>10</v>
@@ -5276,7 +5105,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG30" s="76" t="n">
@@ -5343,37 +5172,32 @@
       <c r="J31" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="74">
-        <f>J31*$T31</f>
-        <v/>
+      <c r="K31" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L31" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M31" s="74">
-        <f>L31*$T31</f>
-        <v/>
+      <c r="M31" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N31" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="74">
-        <f>N31*$T31</f>
-        <v/>
+      <c r="O31" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P31" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" s="74">
-        <f>P31*$T31</f>
-        <v/>
+      <c r="Q31" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R31" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="74">
-        <f>R31*$T31</f>
-        <v/>
+      <c r="S31" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T31" s="75" t="n">
         <v>10</v>
@@ -5429,7 +5253,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG31" s="76" t="n">
@@ -5496,37 +5320,32 @@
       <c r="J32" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K32" s="74">
-        <f>J32*$T32</f>
-        <v/>
+      <c r="K32" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L32" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="74">
-        <f>L32*$T32</f>
-        <v/>
+      <c r="M32" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N32" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O32" s="74">
-        <f>N32*$T32</f>
-        <v/>
+      <c r="O32" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P32" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" s="74">
-        <f>P32*$T32</f>
-        <v/>
+      <c r="Q32" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R32" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="74">
-        <f>R32*$T32</f>
-        <v/>
+      <c r="S32" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T32" s="75" t="n">
         <v>10</v>
@@ -5582,7 +5401,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG32" s="76" t="n">
@@ -5649,37 +5468,32 @@
       <c r="J33" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K33" s="74">
-        <f>J33*$T33</f>
-        <v/>
+      <c r="K33" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L33" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="74">
-        <f>L33*$T33</f>
-        <v/>
+      <c r="M33" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N33" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O33" s="74">
-        <f>N33*$T33</f>
-        <v/>
+      <c r="O33" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P33" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" s="74">
-        <f>P33*$T33</f>
-        <v/>
+      <c r="Q33" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R33" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="74">
-        <f>R33*$T33</f>
-        <v/>
+      <c r="S33" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T33" s="75" t="n">
         <v>10</v>
@@ -5735,7 +5549,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG33" s="76" t="n">
@@ -5802,37 +5616,32 @@
       <c r="J34" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K34" s="74">
-        <f>J34*$T34</f>
-        <v/>
+      <c r="K34" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L34" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="74">
-        <f>L34*$T34</f>
-        <v/>
+      <c r="M34" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N34" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O34" s="74">
-        <f>N34*$T34</f>
-        <v/>
+      <c r="O34" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P34" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="74">
-        <f>P34*$T34</f>
-        <v/>
+      <c r="Q34" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R34" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="74">
-        <f>R34*$T34</f>
-        <v/>
+      <c r="S34" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T34" s="75" t="n">
         <v>10</v>
@@ -5888,7 +5697,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG34" s="76" t="n">
@@ -5955,37 +5764,32 @@
       <c r="J35" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K35" s="74">
-        <f>J35*$T35</f>
-        <v/>
+      <c r="K35" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L35" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="74">
-        <f>L35*$T35</f>
-        <v/>
+      <c r="M35" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N35" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="74">
-        <f>N35*$T35</f>
-        <v/>
+      <c r="O35" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="74">
-        <f>P35*$T35</f>
-        <v/>
+      <c r="Q35" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R35" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="74">
-        <f>R35*$T35</f>
-        <v/>
+      <c r="S35" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T35" s="75" t="n">
         <v>10</v>
@@ -6041,7 +5845,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG35" s="76" t="n">
@@ -6108,37 +5912,32 @@
       <c r="J36" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="74">
-        <f>J36*$T36</f>
-        <v/>
+      <c r="K36" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L36" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="74">
-        <f>L36*$T36</f>
-        <v/>
+      <c r="M36" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O36" s="74">
-        <f>N36*$T36</f>
-        <v/>
+      <c r="O36" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P36" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" s="74">
-        <f>P36*$T36</f>
-        <v/>
+      <c r="Q36" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R36" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="74">
-        <f>R36*$T36</f>
-        <v/>
+      <c r="S36" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T36" s="75" t="n">
         <v>10</v>
@@ -6194,7 +5993,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG36" s="76" t="n">
@@ -6265,37 +6064,32 @@
       <c r="J37" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K37" s="74">
-        <f>J37*$T37</f>
-        <v/>
+      <c r="K37" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L37" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M37" s="74">
-        <f>L37*$T37</f>
-        <v/>
+      <c r="M37" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N37" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O37" s="74">
-        <f>N37*$T37</f>
-        <v/>
+      <c r="O37" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P37" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" s="74">
-        <f>P37*$T37</f>
-        <v/>
+      <c r="Q37" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R37" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="74">
-        <f>R37*$T37</f>
-        <v/>
+      <c r="S37" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T37" s="75" t="n">
         <v>10</v>
@@ -6351,7 +6145,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG37" s="76" t="n">
@@ -6418,37 +6212,32 @@
       <c r="J38" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="74">
-        <f>J38*$T38</f>
-        <v/>
+      <c r="K38" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L38" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M38" s="74">
-        <f>L38*$T38</f>
-        <v/>
+      <c r="M38" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N38" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O38" s="74">
-        <f>N38*$T38</f>
-        <v/>
+      <c r="O38" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P38" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" s="74">
-        <f>P38*$T38</f>
-        <v/>
+      <c r="Q38" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R38" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="74">
-        <f>R38*$T38</f>
-        <v/>
+      <c r="S38" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T38" s="75" t="n">
         <v>10</v>
@@ -6504,7 +6293,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Net Vol. 4 fl oz (118 mL)</t>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
         </is>
       </c>
       <c r="AG38" s="76" t="n">
@@ -6571,37 +6360,32 @@
       <c r="J39" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K39" s="74">
-        <f>J39*$T39</f>
-        <v/>
+      <c r="K39" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L39" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M39" s="74">
-        <f>L39*$T39</f>
-        <v/>
+      <c r="M39" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N39" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O39" s="74">
-        <f>N39*$T39</f>
-        <v/>
+      <c r="O39" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P39" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="74">
-        <f>P39*$T39</f>
-        <v/>
+      <c r="Q39" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R39" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="74">
-        <f>R39*$T39</f>
-        <v/>
+      <c r="S39" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T39" s="75" t="n">
         <v>10</v>
@@ -6634,18 +6418,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA39" s="68">
-        <f>IF(ISNUMBER(Y39),ROUNDDOWN(Y39*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA39" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC39" s="76">
-        <f>IF(AND(ISNUMBER(AA39),ISNUMBER(T39),T39&gt;0),AA39/T39,"")</f>
-        <v/>
+      <c r="AC39" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD39" s="43" t="inlineStr">
         <is>
@@ -6657,17 +6439,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF39">
-        <f>"Net Vol. "&amp;TEXT(Y39,"0.##")&amp;" fl oz ("&amp;TEXT(AA39,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG39" s="76">
-        <f>IF(AND(ISNUMBER(Y39),ISNUMBER(T39),T39&gt;0),Y39/T39,"")</f>
-        <v/>
-      </c>
-      <c r="AH39">
-        <f>IF(AG39="","",TEXT(AG39,"0.##")&amp;" fl oz ("&amp;TEXT(AC39,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG39" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI39" s="43" t="inlineStr">
         <is>
@@ -6725,37 +6508,32 @@
       <c r="J40" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K40" s="74">
-        <f>J40*$T40</f>
-        <v/>
+      <c r="K40" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L40" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M40" s="74">
-        <f>L40*$T40</f>
-        <v/>
+      <c r="M40" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N40" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O40" s="74">
-        <f>N40*$T40</f>
-        <v/>
+      <c r="O40" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="74">
-        <f>P40*$T40</f>
-        <v/>
+      <c r="Q40" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R40" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="74">
-        <f>R40*$T40</f>
-        <v/>
+      <c r="S40" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T40" s="75" t="n">
         <v>10</v>
@@ -6788,18 +6566,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA40" s="68">
-        <f>IF(ISNUMBER(Y40),ROUNDDOWN(Y40*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA40" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC40" s="76">
-        <f>IF(AND(ISNUMBER(AA40),ISNUMBER(T40),T40&gt;0),AA40/T40,"")</f>
-        <v/>
+      <c r="AC40" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD40" s="43" t="inlineStr">
         <is>
@@ -6811,17 +6587,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF40">
-        <f>"Net Vol. "&amp;TEXT(Y40,"0.##")&amp;" fl oz ("&amp;TEXT(AA40,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG40" s="76">
-        <f>IF(AND(ISNUMBER(Y40),ISNUMBER(T40),T40&gt;0),Y40/T40,"")</f>
-        <v/>
-      </c>
-      <c r="AH40">
-        <f>IF(AG40="","",TEXT(AG40,"0.##")&amp;" fl oz ("&amp;TEXT(AC40,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG40" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI40" s="43" t="inlineStr">
         <is>
@@ -6879,37 +6656,32 @@
       <c r="J41" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K41" s="74">
-        <f>J41*$T41</f>
-        <v/>
+      <c r="K41" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L41" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M41" s="74">
-        <f>L41*$T41</f>
-        <v/>
+      <c r="M41" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N41" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O41" s="74">
-        <f>N41*$T41</f>
-        <v/>
+      <c r="O41" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P41" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" s="74">
-        <f>P41*$T41</f>
-        <v/>
+      <c r="Q41" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R41" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="74">
-        <f>R41*$T41</f>
-        <v/>
+      <c r="S41" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T41" s="75" t="n">
         <v>10</v>
@@ -6942,18 +6714,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA41" s="68">
-        <f>IF(ISNUMBER(Y41),ROUNDDOWN(Y41*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA41" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC41" s="76">
-        <f>IF(AND(ISNUMBER(AA41),ISNUMBER(T41),T41&gt;0),AA41/T41,"")</f>
-        <v/>
+      <c r="AC41" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD41" s="43" t="inlineStr">
         <is>
@@ -6965,17 +6735,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF41">
-        <f>"Net Vol. "&amp;TEXT(Y41,"0.##")&amp;" fl oz ("&amp;TEXT(AA41,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG41" s="76">
-        <f>IF(AND(ISNUMBER(Y41),ISNUMBER(T41),T41&gt;0),Y41/T41,"")</f>
-        <v/>
-      </c>
-      <c r="AH41">
-        <f>IF(AG41="","",TEXT(AG41,"0.##")&amp;" fl oz ("&amp;TEXT(AC41,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG41" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI41" s="43" t="inlineStr">
         <is>
@@ -7033,37 +6804,32 @@
       <c r="J42" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K42" s="74">
-        <f>J42*$T42</f>
-        <v/>
+      <c r="K42" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L42" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M42" s="74">
-        <f>L42*$T42</f>
-        <v/>
+      <c r="M42" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N42" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O42" s="74">
-        <f>N42*$T42</f>
-        <v/>
+      <c r="O42" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P42" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="74">
-        <f>P42*$T42</f>
-        <v/>
+      <c r="Q42" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R42" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="74">
-        <f>R42*$T42</f>
-        <v/>
+      <c r="S42" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T42" s="75" t="n">
         <v>10</v>
@@ -7096,18 +6862,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA42" s="68">
-        <f>IF(ISNUMBER(Y42),ROUNDDOWN(Y42*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA42" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC42" s="76">
-        <f>IF(AND(ISNUMBER(AA42),ISNUMBER(T42),T42&gt;0),AA42/T42,"")</f>
-        <v/>
+      <c r="AC42" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD42" s="43" t="inlineStr">
         <is>
@@ -7119,17 +6883,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF42">
-        <f>"Net Vol. "&amp;TEXT(Y42,"0.##")&amp;" fl oz ("&amp;TEXT(AA42,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG42" s="76">
-        <f>IF(AND(ISNUMBER(Y42),ISNUMBER(T42),T42&gt;0),Y42/T42,"")</f>
-        <v/>
-      </c>
-      <c r="AH42">
-        <f>IF(AG42="","",TEXT(AG42,"0.##")&amp;" fl oz ("&amp;TEXT(AC42,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG42" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI42" s="43" t="inlineStr">
         <is>
@@ -7187,37 +6952,32 @@
       <c r="J43" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K43" s="74">
-        <f>J43*$T43</f>
-        <v/>
+      <c r="K43" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L43" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M43" s="74">
-        <f>L43*$T43</f>
-        <v/>
+      <c r="M43" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N43" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O43" s="74">
-        <f>N43*$T43</f>
-        <v/>
+      <c r="O43" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P43" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="74">
-        <f>P43*$T43</f>
-        <v/>
+      <c r="Q43" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R43" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="74">
-        <f>R43*$T43</f>
-        <v/>
+      <c r="S43" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T43" s="75" t="n">
         <v>10</v>
@@ -7250,18 +7010,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA43" s="68">
-        <f>IF(ISNUMBER(Y43),ROUNDDOWN(Y43*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA43" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC43" s="76">
-        <f>IF(AND(ISNUMBER(AA43),ISNUMBER(T43),T43&gt;0),AA43/T43,"")</f>
-        <v/>
+      <c r="AC43" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD43" s="43" t="inlineStr">
         <is>
@@ -7273,17 +7031,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF43">
-        <f>"Net Vol. "&amp;TEXT(Y43,"0.##")&amp;" fl oz ("&amp;TEXT(AA43,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG43" s="76">
-        <f>IF(AND(ISNUMBER(Y43),ISNUMBER(T43),T43&gt;0),Y43/T43,"")</f>
-        <v/>
-      </c>
-      <c r="AH43">
-        <f>IF(AG43="","",TEXT(AG43,"0.##")&amp;" fl oz ("&amp;TEXT(AC43,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG43" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI43" s="43" t="inlineStr">
         <is>
@@ -7341,37 +7100,32 @@
       <c r="J44" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K44" s="74">
-        <f>J44*$T44</f>
-        <v/>
+      <c r="K44" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L44" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="74">
-        <f>L44*$T44</f>
-        <v/>
+      <c r="M44" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O44" s="74">
-        <f>N44*$T44</f>
-        <v/>
+      <c r="O44" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P44" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" s="74">
-        <f>P44*$T44</f>
-        <v/>
+      <c r="Q44" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R44" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="74">
-        <f>R44*$T44</f>
-        <v/>
+      <c r="S44" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T44" s="75" t="n">
         <v>10</v>
@@ -7404,18 +7158,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA44" s="68">
-        <f>IF(ISNUMBER(Y44),ROUNDDOWN(Y44*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA44" s="68" t="n">
+        <v>473</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC44" s="76">
-        <f>IF(AND(ISNUMBER(AA44),ISNUMBER(T44),T44&gt;0),AA44/T44,"")</f>
-        <v/>
+      <c r="AC44" s="76" t="n">
+        <v>47.3</v>
       </c>
       <c r="AD44" s="43" t="inlineStr">
         <is>
@@ -7427,17 +7179,18 @@
           <t>https://maryjonescannabis.com/</t>
         </is>
       </c>
-      <c r="AF44">
-        <f>"Net Vol. "&amp;TEXT(Y44,"0.##")&amp;" fl oz ("&amp;TEXT(AA44,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG44" s="76">
-        <f>IF(AND(ISNUMBER(Y44),ISNUMBER(T44),T44&gt;0),Y44/T44,"")</f>
-        <v/>
-      </c>
-      <c r="AH44">
-        <f>IF(AG44="","",TEXT(AG44,"0.##")&amp;" fl oz ("&amp;TEXT(AC44,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Net Vol. 16. fl oz (473. mL)</t>
+        </is>
+      </c>
+      <c r="AG44" s="76" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>1.6 fl oz (47.3 mL)</t>
+        </is>
       </c>
       <c r="AI44" s="43" t="inlineStr">
         <is>
@@ -7495,37 +7248,32 @@
       <c r="J45" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K45" s="74">
-        <f>J45*$T45</f>
-        <v/>
+      <c r="K45" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L45" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M45" s="74">
-        <f>L45*$T45</f>
-        <v/>
+      <c r="M45" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N45" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O45" s="74">
-        <f>N45*$T45</f>
-        <v/>
+      <c r="O45" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P45" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" s="74">
-        <f>P45*$T45</f>
-        <v/>
+      <c r="Q45" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R45" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="74">
-        <f>R45*$T45</f>
-        <v/>
+      <c r="S45" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T45" s="75" t="n">
         <v>10</v>
@@ -7558,18 +7306,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA45" s="68">
-        <f>IF(ISNUMBER(Y45),ROUNDDOWN(Y45*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA45" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC45" s="76">
-        <f>IF(AND(ISNUMBER(AA45),ISNUMBER(T45),T45&gt;0),AA45/T45,"")</f>
-        <v/>
+      <c r="AC45" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD45" s="43" t="inlineStr">
         <is>
@@ -7581,17 +7327,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF45">
-        <f>"Net Vol. "&amp;TEXT(Y45,"0.##")&amp;" fl oz ("&amp;TEXT(AA45,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG45" s="76">
-        <f>IF(AND(ISNUMBER(Y45),ISNUMBER(T45),T45&gt;0),Y45/T45,"")</f>
-        <v/>
-      </c>
-      <c r="AH45">
-        <f>IF(AG45="","",TEXT(AG45,"0.##")&amp;" fl oz ("&amp;TEXT(AC45,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG45" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI45" s="43" t="inlineStr">
         <is>
@@ -7649,37 +7396,32 @@
       <c r="J46" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K46" s="74">
-        <f>J46*$T46</f>
-        <v/>
+      <c r="K46" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L46" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M46" s="74">
-        <f>L46*$T46</f>
-        <v/>
+      <c r="M46" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N46" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="74">
-        <f>N46*$T46</f>
-        <v/>
+      <c r="O46" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P46" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" s="74">
-        <f>P46*$T46</f>
-        <v/>
+      <c r="Q46" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R46" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S46" s="74">
-        <f>R46*$T46</f>
-        <v/>
+      <c r="S46" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T46" s="75" t="n">
         <v>10</v>
@@ -7712,18 +7454,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA46" s="68">
-        <f>IF(ISNUMBER(Y46),ROUNDDOWN(Y46*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA46" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC46" s="76">
-        <f>IF(AND(ISNUMBER(AA46),ISNUMBER(T46),T46&gt;0),AA46/T46,"")</f>
-        <v/>
+      <c r="AC46" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD46" s="43" t="inlineStr">
         <is>
@@ -7735,17 +7475,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF46">
-        <f>"Net Vol. "&amp;TEXT(Y46,"0.##")&amp;" fl oz ("&amp;TEXT(AA46,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG46" s="76">
-        <f>IF(AND(ISNUMBER(Y46),ISNUMBER(T46),T46&gt;0),Y46/T46,"")</f>
-        <v/>
-      </c>
-      <c r="AH46">
-        <f>IF(AG46="","",TEXT(AG46,"0.##")&amp;" fl oz ("&amp;TEXT(AC46,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG46" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI46" s="43" t="inlineStr">
         <is>
@@ -7803,37 +7544,32 @@
       <c r="J47" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K47" s="74">
-        <f>J47*$T47</f>
-        <v/>
+      <c r="K47" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L47" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M47" s="74">
-        <f>L47*$T47</f>
-        <v/>
+      <c r="M47" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N47" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O47" s="74">
-        <f>N47*$T47</f>
-        <v/>
+      <c r="O47" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P47" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" s="74">
-        <f>P47*$T47</f>
-        <v/>
+      <c r="Q47" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R47" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S47" s="74">
-        <f>R47*$T47</f>
-        <v/>
+      <c r="S47" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T47" s="75" t="n">
         <v>10</v>
@@ -7866,18 +7602,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA47" s="68">
-        <f>IF(ISNUMBER(Y47),ROUNDDOWN(Y47*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA47" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC47" s="76">
-        <f>IF(AND(ISNUMBER(AA47),ISNUMBER(T47),T47&gt;0),AA47/T47,"")</f>
-        <v/>
+      <c r="AC47" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD47" s="43" t="inlineStr">
         <is>
@@ -7889,17 +7623,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF47">
-        <f>"Net Vol. "&amp;TEXT(Y47,"0.##")&amp;" fl oz ("&amp;TEXT(AA47,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG47" s="76">
-        <f>IF(AND(ISNUMBER(Y47),ISNUMBER(T47),T47&gt;0),Y47/T47,"")</f>
-        <v/>
-      </c>
-      <c r="AH47">
-        <f>IF(AG47="","",TEXT(AG47,"0.##")&amp;" fl oz ("&amp;TEXT(AC47,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG47" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI47" s="43" t="inlineStr">
         <is>
@@ -7957,37 +7692,32 @@
       <c r="J48" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K48" s="74">
-        <f>J48*$T48</f>
-        <v/>
+      <c r="K48" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L48" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="M48" s="74">
-        <f>L48*$T48</f>
-        <v/>
+      <c r="M48" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="N48" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O48" s="74">
-        <f>N48*$T48</f>
-        <v/>
+      <c r="O48" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P48" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" s="74">
-        <f>P48*$T48</f>
-        <v/>
+      <c r="Q48" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R48" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="74">
-        <f>R48*$T48</f>
-        <v/>
+      <c r="S48" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T48" s="75" t="n">
         <v>10</v>
@@ -8020,18 +7750,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA48" s="68">
-        <f>IF(ISNUMBER(Y48),ROUNDDOWN(Y48*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA48" s="68" t="n">
+        <v>118</v>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC48" s="76">
-        <f>IF(AND(ISNUMBER(AA48),ISNUMBER(T48),T48&gt;0),AA48/T48,"")</f>
-        <v/>
+      <c r="AC48" s="76" t="n">
+        <v>11.8</v>
       </c>
       <c r="AD48" s="43" t="inlineStr">
         <is>
@@ -8043,17 +7771,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF48">
-        <f>"Net Vol. "&amp;TEXT(Y48,"0.##")&amp;" fl oz ("&amp;TEXT(AA48,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG48" s="76">
-        <f>IF(AND(ISNUMBER(Y48),ISNUMBER(T48),T48&gt;0),Y48/T48,"")</f>
-        <v/>
-      </c>
-      <c r="AH48">
-        <f>IF(AG48="","",TEXT(AG48,"0.##")&amp;" fl oz ("&amp;TEXT(AC48,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
+        </is>
+      </c>
+      <c r="AG48" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>0.4 fl oz (11.8 mL)</t>
+        </is>
       </c>
       <c r="AI48" s="43" t="inlineStr">
         <is>
@@ -8115,37 +7844,32 @@
       <c r="J49" s="74" t="n">
         <v>5</v>
       </c>
-      <c r="K49" s="74">
-        <f>J49*$T49</f>
-        <v/>
+      <c r="K49" s="74" t="n">
+        <v>50</v>
       </c>
       <c r="L49" s="74" t="n">
         <v>2.5</v>
       </c>
-      <c r="M49" s="74">
-        <f>L49*$T49</f>
-        <v/>
+      <c r="M49" s="74" t="n">
+        <v>25</v>
       </c>
       <c r="N49" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O49" s="74">
-        <f>N49*$T49</f>
-        <v/>
+      <c r="O49" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P49" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="74">
-        <f>P49*$T49</f>
-        <v/>
+      <c r="Q49" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R49" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="74">
-        <f>R49*$T49</f>
-        <v/>
+      <c r="S49" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T49" s="75" t="n">
         <v>10</v>
@@ -8178,18 +7902,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA49" s="68">
-        <f>IF(ISNUMBER(Y49),ROUNDDOWN(Y49*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA49" s="68" t="n">
+        <v>118</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC49" s="76">
-        <f>IF(AND(ISNUMBER(AA49),ISNUMBER(T49),T49&gt;0),AA49/T49,"")</f>
-        <v/>
+      <c r="AC49" s="76" t="n">
+        <v>11.8</v>
       </c>
       <c r="AD49" s="43" t="inlineStr">
         <is>
@@ -8201,17 +7923,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF49">
-        <f>"Net Vol. "&amp;TEXT(Y49,"0.##")&amp;" fl oz ("&amp;TEXT(AA49,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG49" s="76">
-        <f>IF(AND(ISNUMBER(Y49),ISNUMBER(T49),T49&gt;0),Y49/T49,"")</f>
-        <v/>
-      </c>
-      <c r="AH49">
-        <f>IF(AG49="","",TEXT(AG49,"0.##")&amp;" fl oz ("&amp;TEXT(AC49,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Net Vol. 4. fl oz (118. mL)</t>
+        </is>
+      </c>
+      <c r="AG49" s="76" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>0.4 fl oz (11.8 mL)</t>
+        </is>
       </c>
       <c r="AI49" s="43" t="inlineStr">
         <is>
@@ -8273,37 +7996,32 @@
       <c r="J50" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="K50" s="74">
-        <f>J50*$T50</f>
-        <v/>
+      <c r="K50" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="L50" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M50" s="74">
-        <f>L50*$T50</f>
-        <v/>
+      <c r="M50" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N50" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O50" s="74">
-        <f>N50*$T50</f>
-        <v/>
+      <c r="O50" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P50" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="74">
-        <f>P50*$T50</f>
-        <v/>
+      <c r="Q50" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R50" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="74">
-        <f>R50*$T50</f>
-        <v/>
+      <c r="S50" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T50" s="75" t="n">
         <v>10</v>
@@ -8336,18 +8054,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA50" s="68">
-        <f>IF(ISNUMBER(Y50),ROUNDDOWN(Y50*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA50" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC50" s="76">
-        <f>IF(AND(ISNUMBER(AA50),ISNUMBER(T50),T50&gt;0),AA50/T50,"")</f>
-        <v/>
+      <c r="AC50" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD50" s="43" t="inlineStr">
         <is>
@@ -8359,17 +8075,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF50">
-        <f>"Net Vol. "&amp;TEXT(Y50,"0.##")&amp;" fl oz ("&amp;TEXT(AA50,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG50" s="76">
-        <f>IF(AND(ISNUMBER(Y50),ISNUMBER(T50),T50&gt;0),Y50/T50,"")</f>
-        <v/>
-      </c>
-      <c r="AH50">
-        <f>IF(AG50="","",TEXT(AG50,"0.##")&amp;" fl oz ("&amp;TEXT(AC50,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG50" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI50" s="43" t="inlineStr">
         <is>
@@ -8427,37 +8144,32 @@
       <c r="J51" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="74">
-        <f>J51*$T51</f>
-        <v/>
+      <c r="K51" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="L51" s="74" t="n">
         <v>10</v>
       </c>
-      <c r="M51" s="74">
-        <f>L51*$T51</f>
-        <v/>
+      <c r="M51" s="74" t="n">
+        <v>100</v>
       </c>
       <c r="N51" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="O51" s="74">
-        <f>N51*$T51</f>
-        <v/>
+      <c r="O51" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="P51" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" s="74">
-        <f>P51*$T51</f>
-        <v/>
+      <c r="Q51" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="R51" s="74" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="74">
-        <f>R51*$T51</f>
-        <v/>
+      <c r="S51" s="74" t="n">
+        <v>0</v>
       </c>
       <c r="T51" s="75" t="n">
         <v>10</v>
@@ -8490,18 +8202,16 @@
           <t>fl oz</t>
         </is>
       </c>
-      <c r="AA51" s="68">
-        <f>IF(ISNUMBER(Y51),ROUNDDOWN(Y51*29.5735295625,0),"")</f>
-        <v/>
+      <c r="AA51" s="68" t="n">
+        <v>354</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
           <t>mL</t>
         </is>
       </c>
-      <c r="AC51" s="76">
-        <f>IF(AND(ISNUMBER(AA51),ISNUMBER(T51),T51&gt;0),AA51/T51,"")</f>
-        <v/>
+      <c r="AC51" s="76" t="n">
+        <v>35.4</v>
       </c>
       <c r="AD51" s="43" t="inlineStr">
         <is>
@@ -8513,17 +8223,18 @@
           <t>Mock extension based on Ray's Lemonade's established product format/flavor direction</t>
         </is>
       </c>
-      <c r="AF51">
-        <f>"Net Vol. "&amp;TEXT(Y51,"0.##")&amp;" fl oz ("&amp;TEXT(AA51,"0.#")&amp;" mL)"</f>
-        <v/>
-      </c>
-      <c r="AG51" s="76">
-        <f>IF(AND(ISNUMBER(Y51),ISNUMBER(T51),T51&gt;0),Y51/T51,"")</f>
-        <v/>
-      </c>
-      <c r="AH51">
-        <f>IF(AG51="","",TEXT(AG51,"0.##")&amp;" fl oz ("&amp;TEXT(AC51,"0.#")&amp;" mL)")</f>
-        <v/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Net Vol. 12. fl oz (354. mL)</t>
+        </is>
+      </c>
+      <c r="AG51" s="76" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>1.2 fl oz (35.4 mL)</t>
+        </is>
       </c>
       <c r="AI51" s="43" t="inlineStr">
         <is>

--- a/reference/origins/product info/WA_Drinks_Regulatory_Audited.xlsx
+++ b/reference/origins/product info/WA_Drinks_Regulatory_Audited.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="D2" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E2" s="58" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="D18" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E18" s="58" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="D20" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E20" s="58" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="D21" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E21" s="58" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="D22" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E22" s="58" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="D23" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E23" s="58" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="D24" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E24" s="58" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D25" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E25" s="58" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="D26" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E26" s="58" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="D27" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E27" s="58" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="D28" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E28" s="58" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="D32" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E32" s="58" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="D33" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E33" s="58" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D34" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E34" s="58" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="D35" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E35" s="58" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D36" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E36" s="58" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="D39" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E39" s="58" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D40" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E40" s="58" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="D41" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E41" s="58" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="D42" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E42" s="58" t="inlineStr">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="D43" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E43" s="58" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D44" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E44" s="58" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="D45" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E45" s="58" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="D46" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E46" s="58" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="D47" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E47" s="58" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="D48" s="58" t="inlineStr">
         <is>
-          <t>THC Only</t>
+          <t>THC</t>
         </is>
       </c>
       <c r="E48" s="58" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="B4" s="43" t="inlineStr">
         <is>
-          <t>THC Only / Blend / CBD → Drink / Shot / Seltzer / Sorbet / Honey</t>
+          <t>THC / Blend / CBD → Drink / Shot / Seltzer / Sorbet / Honey</t>
         </is>
       </c>
     </row>
@@ -8496,6 +8496,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="43" t="inlineStr">
         <is>
